--- a/Dataset_S1.xlsx
+++ b/Dataset_S1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mingyang/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mingyang/MyDrive/writing/2023_aging_cell.turnover/2023-02-28/PNAS_submission_0308/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67DCA885-7157-3241-A862-7945E3396D64}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5064DF88-464D-CB44-940F-4CF9C6B3F6E5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3220" yWindow="520" windowWidth="33520" windowHeight="26300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -753,7 +753,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -933,18 +933,6 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -1115,18 +1103,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2695,32 +2677,32 @@
       <c r="J39" s="2"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="2">
         <v>9400</v>
       </c>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3">
+      <c r="D40" s="2"/>
+      <c r="E40" s="2">
         <v>9400</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="2">
         <v>764</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="2">
         <v>818</v>
       </c>
-      <c r="I40" s="3">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="s">
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>61</v>
       </c>
     </row>
@@ -4429,31 +4411,31 @@
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C96" s="3">
+      <c r="C96" s="2">
         <v>323.04667910000001</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="D96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="2">
         <v>102</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96" s="2">
         <v>163</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="2">
         <v>1</v>
       </c>
       <c r="J96" s="2" t="s">
@@ -4885,34 +4867,34 @@
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111" s="2">
         <v>800</v>
       </c>
-      <c r="D111" s="4">
+      <c r="D111" s="2">
         <v>60</v>
       </c>
-      <c r="E111" s="4">
+      <c r="E111" s="2">
         <v>60</v>
       </c>
-      <c r="F111" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G111" s="4">
+      <c r="F111" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G111" s="2">
         <v>91</v>
       </c>
-      <c r="H111" s="4">
+      <c r="H111" s="2">
         <v>214</v>
       </c>
-      <c r="I111" s="4">
+      <c r="I111" s="2">
         <v>1</v>
       </c>
-      <c r="J111" s="4"/>
+      <c r="J111" s="2"/>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
@@ -5441,29 +5423,29 @@
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4">
+      <c r="C129" s="2"/>
+      <c r="D129" s="2">
         <v>3.8</v>
       </c>
-      <c r="E129" s="4">
+      <c r="E129" s="2">
         <v>3.8</v>
       </c>
-      <c r="F129" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G129" s="4">
+      <c r="F129" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G129" s="2">
         <v>253</v>
       </c>
-      <c r="H129" s="4">
+      <c r="H129" s="2">
         <v>565</v>
       </c>
-      <c r="I129" s="4">
+      <c r="I129" s="2">
         <v>1</v>
       </c>
       <c r="J129" s="2"/>
@@ -5561,32 +5543,32 @@
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4">
+      <c r="C133" s="2"/>
+      <c r="D133" s="2">
         <v>3.8</v>
       </c>
-      <c r="E133" s="4">
+      <c r="E133" s="2">
         <v>3.8</v>
       </c>
-      <c r="F133" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G133" s="4">
+      <c r="F133" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G133" s="2">
         <v>422</v>
       </c>
-      <c r="H133" s="4">
+      <c r="H133" s="2">
         <v>335</v>
       </c>
-      <c r="I133" s="4">
+      <c r="I133" s="2">
         <v>1</v>
       </c>
-      <c r="J133" s="4" t="s">
+      <c r="J133" s="2" t="s">
         <v>185</v>
       </c>
     </row>
